--- a/docs/downloads/经营分_津河省区__津西片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_津河省区__津西片区_2026-10-18.xlsx
@@ -709,7 +709,7 @@
         <v>45</v>
       </c>
       <c r="I2" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1478,14 +1478,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H11" t="n">
         <v>87</v>
       </c>
       <c r="I11" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1639,17 +1639,17 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>7477819440306849833</t>
+          <t>6601138733221677069</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>丽柏酒店（天津站津湾广场店）</t>
+          <t>锦江之星天津南站酒店</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>丽柏酒店(天津站津湾广场店)</t>
+          <t>锦江之星(天津南站酒店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1675,13 +1675,13 @@
         <v>10</v>
       </c>
       <c r="M13" t="n">
+        <v>20</v>
+      </c>
+      <c r="N13" t="n">
+        <v>30</v>
+      </c>
+      <c r="O13" t="n">
         <v>25</v>
-      </c>
-      <c r="N13" t="n">
-        <v>30</v>
-      </c>
-      <c r="O13" t="n">
-        <v>20</v>
       </c>
       <c r="P13" t="n">
         <v>30</v>
@@ -1727,17 +1727,17 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>6601138733221677069</t>
+          <t>6871422071910451214</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>锦江之星天津南站酒店</t>
+          <t>喆啡酒店（天津中北永旺购物中心店）</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>锦江之星(天津南站酒店)</t>
+          <t>喆啡酒店(天津中北永旺购物中心宜家店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1763,19 +1763,19 @@
         <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N14" t="n">
         <v>30</v>
       </c>
       <c r="O14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P14" t="n">
         <v>30</v>
       </c>
       <c r="Q14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R14" t="n">
         <v>30</v>
@@ -1815,17 +1815,17 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>6871422071910451214</t>
+          <t>7131688853400012831</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>喆啡酒店（天津中北永旺购物中心店）</t>
+          <t>喆啡酒店（天津梅江会展中心芦北路地铁站店）</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>喆啡酒店(天津中北永旺购物中心宜家店)</t>
+          <t>喆啡酒店(天津梅江会展中心店)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1837,7 +1837,7 @@
         <v>92</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1857,13 +1857,13 @@
         <v>30</v>
       </c>
       <c r="O15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P15" t="n">
         <v>30</v>
       </c>
       <c r="Q15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R15" t="n">
         <v>30</v>
@@ -1903,17 +1903,17 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>7131688853400012831</t>
+          <t>6952624256819660831</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>喆啡酒店（天津梅江会展中心芦北路地铁站店）</t>
+          <t>维也纳智好酒店（天津火车站海河津湾店）</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>喆啡酒店(天津梅江会展中心店)</t>
+          <t>维也纳智好酒店(天津火车站海河津湾店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1925,7 +1925,7 @@
         <v>92</v>
       </c>
       <c r="I16" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1986,22 +1986,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>廊坊市</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>6952624256819660831</t>
+          <t>7365317579419682827</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>维也纳智好酒店（天津火车站海河津湾店）</t>
+          <t>霸州胜芳高铁站希岸Deluxe酒店</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>维也纳智好酒店(天津火车站海河津湾店)</t>
+          <t>希岸Deluxe酒店(霸州胜芳高铁站店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -2027,13 +2027,13 @@
         <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N17" t="n">
         <v>30</v>
       </c>
       <c r="O17" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P17" t="n">
         <v>30</v>
@@ -2074,27 +2074,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>廊坊市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>7365317579419682827</t>
+          <t>6960661316453271588</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>霸州胜芳高铁站希岸Deluxe酒店</t>
+          <t>麗枫酒店·天津华苑店</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>希岸Deluxe酒店(霸州胜芳高铁站店)</t>
+          <t>麗枫酒店(天津华苑店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -2115,19 +2115,19 @@
         <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N18" t="n">
         <v>30</v>
       </c>
       <c r="O18" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P18" t="n">
         <v>30</v>
       </c>
       <c r="Q18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R18" t="n">
         <v>30</v>
@@ -2162,22 +2162,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>廊坊市</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>6960661316453271588</t>
+          <t>6735966128167766029</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>麗枫酒店·天津华苑店</t>
+          <t>麗枫酒店·廊坊大城鑫达新天地广场店</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津华苑店)</t>
+          <t>麗枫酒店(廊坊大城鑫达新天地广场店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2250,34 +2250,34 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>廊坊市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>6735966128167766029</t>
+          <t>7477819440306849833</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>麗枫酒店·廊坊大城鑫达新天地广场店</t>
+          <t>丽柏酒店（天津站津湾广场店）</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>麗枫酒店(廊坊大城鑫达新天地广场店)</t>
+          <t>丽柏酒店(天津站津湾广场店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N20" t="n">
         <v>30</v>
@@ -2343,17 +2343,17 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>6601137259485857799</t>
+          <t>7151585570098808840</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>7天酒店（天津交通学院曹庄地铁站店）</t>
+          <t>喆啡酒店(静海团泊湖温泉仁爱学院大邱庄店)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>7天连锁酒店(天津交通学院曹庄地铁站店)</t>
+          <t>喆啡酒店(天津静海团泊湖大邱庄店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2362,14 +2362,14 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -2379,19 +2379,19 @@
         <v>10</v>
       </c>
       <c r="M21" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N21" t="n">
         <v>30</v>
       </c>
       <c r="O21" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P21" t="n">
         <v>30</v>
       </c>
       <c r="Q21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R21" t="n">
         <v>30</v>
@@ -2431,17 +2431,17 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>7151585570098808840</t>
+          <t>7254746060860426279</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>喆啡酒店(静海团泊湖温泉仁爱学院大邱庄店)</t>
+          <t>天津静海万达广场丽柏酒店</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>喆啡酒店(天津静海团泊湖大邱庄店)</t>
+          <t>丽柏酒店(天津静海万达广场店)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2514,27 +2514,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>廊坊市</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>7254746060860426279</t>
+          <t>7024384426881353742</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>天津静海万达广场丽柏酒店</t>
+          <t>希岸酒店大城红木城店</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>丽柏酒店(天津静海万达广场店)</t>
+          <t>希岸酒店(大城红木城店)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -2607,33 +2607,33 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>7024384426881353742</t>
+          <t>6647007075144665095</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>希岸酒店大城红木城店</t>
+          <t>麗枫酒店·霸州胜芳店</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>希岸酒店(大城红木城店)</t>
+          <t>丽枫酒店(霸州胜芳店)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H24" t="n">
         <v>97</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -2649,13 +2649,13 @@
         <v>30</v>
       </c>
       <c r="O24" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P24" t="n">
         <v>30</v>
       </c>
       <c r="Q24" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="R24" t="n">
         <v>30</v>
@@ -2690,22 +2690,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>廊坊市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>6647007075144665095</t>
+          <t>6601134591287756814</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>麗枫酒店·霸州胜芳店</t>
+          <t>锦江之星(天津新开路店)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>丽枫酒店(霸州胜芳店)</t>
+          <t>锦江之星(天津新开路店)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2714,14 +2714,14 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,附加分,拿收益</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -2737,19 +2737,19 @@
         <v>30</v>
       </c>
       <c r="O25" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P25" t="n">
         <v>30</v>
       </c>
       <c r="Q25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R25" t="n">
         <v>30</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T25" t="n">
         <v>20</v>
@@ -2783,17 +2783,17 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>6601134591287756814</t>
+          <t>6601137259485857799</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>锦江之星(天津新开路店)</t>
+          <t>7天酒店（天津交通学院曹庄地铁站店）</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>锦江之星(天津新开路店)</t>
+          <t>7天连锁酒店(天津交通学院曹庄地铁站店)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2802,14 +2802,14 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I26" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>稳房源,附加分,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2819,25 +2819,25 @@
         <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N26" t="n">
         <v>30</v>
       </c>
       <c r="O26" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P26" t="n">
         <v>30</v>
       </c>
       <c r="Q26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R26" t="n">
         <v>30</v>
       </c>
       <c r="S26" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="T26" t="n">
         <v>20</v>
@@ -2871,17 +2871,17 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>6601172604214577160</t>
+          <t>6687194211739011080</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IU酒店·天津梅江会展大寺镇政府店</t>
+          <t>IU酒店（天津侯台城建大学海泰工业园店）</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>iu酒店(天津梅江会展大寺店)</t>
+          <t>IU酒店(天津侯台城建大学海泰工业园店)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2893,7 +2893,7 @@
         <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2954,22 +2954,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>廊坊市</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>6687194211739011080</t>
+          <t>7443310402835843122</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IU酒店（天津侯台城建大学海泰工业园店）</t>
+          <t>锦江之星酒店（大城县政府红木城店）</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>IU酒店(天津侯台城建大学海泰工业园店)</t>
+          <t>锦江之星酒店(大城县政府红木城店)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2981,7 +2981,7 @@
         <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -3042,22 +3042,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>廊坊市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>7443310402835843122</t>
+          <t>7081335014855542792</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>锦江之星酒店（大城县政府红木城店）</t>
+          <t>喆啡酒店（天津火车站北广场店）</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>锦江之星酒店(大城县政府红木城店)</t>
+          <t>喆啡酒店(天津火车站北广场店)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3066,14 +3066,14 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -3083,13 +3083,13 @@
         <v>10</v>
       </c>
       <c r="M29" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N29" t="n">
         <v>30</v>
       </c>
       <c r="O29" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P29" t="n">
         <v>30</v>
@@ -3135,17 +3135,17 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>7081335014855542792</t>
+          <t>6601172604214577160</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>喆啡酒店（天津火车站北广场店）</t>
+          <t>IU酒店·天津梅江会展大寺镇政府店</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>喆啡酒店(天津火车站北广场店)</t>
+          <t>iu酒店(天津梅江会展大寺店)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3154,14 +3154,14 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -3171,19 +3171,19 @@
         <v>10</v>
       </c>
       <c r="M30" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N30" t="n">
         <v>30</v>
       </c>
       <c r="O30" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P30" t="n">
         <v>30</v>
       </c>
       <c r="Q30" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R30" t="n">
         <v>30</v>
@@ -3421,7 +3421,7 @@
         <v>107</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
